--- a/data/trans_orig/IP16_n_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>17078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15377</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>25042</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21927</t>
+          <t>22265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44420</t>
+          <t>44780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>11329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21574</t>
+          <t>21205</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>17231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35703</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>20442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29802</t>
+          <t>30318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23720</t>
+          <t>24075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33274</t>
+          <t>32980</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47249</t>
+          <t>46768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60808</t>
+          <t>60612</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11861</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>11740</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22028</t>
+          <t>21247</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18891</t>
+          <t>18540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31380</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20418</t>
+          <t>20587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>23383</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41395</t>
+          <t>41746</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>69,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15670</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>23501</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22671</t>
+          <t>22882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36180</t>
+          <t>35146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18265</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26124</t>
+          <t>25588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28314</t>
+          <t>29348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41823</t>
+          <t>41612</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39093</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56965</t>
+          <t>57125</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>48140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65808</t>
+          <t>66271</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93218</t>
+          <t>92190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119813</t>
+          <t>118258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>68180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>85591</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78111</t>
+          <t>77648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96121</t>
+          <t>95779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>149411</t>
+          <t>150966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176006</t>
+          <t>177034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13089</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>21303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18357</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>26668</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23579</t>
+          <t>23596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>31485</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44405</t>
+          <t>44567</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56290</t>
+          <t>56567</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31434</t>
+          <t>31903</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38881</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30982</t>
+          <t>30881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38286</t>
+          <t>38331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65716</t>
+          <t>65990</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76018</t>
+          <t>76073</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>23153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29878</t>
+          <t>29965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29605</t>
+          <t>29574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54674</t>
+          <t>54709</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64046</t>
+          <t>64108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11214</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>30367</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38488</t>
+          <t>38687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34757</t>
+          <t>34859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43528</t>
+          <t>43258</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68547</t>
+          <t>67308</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79731</t>
+          <t>80013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>18904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29427</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36973</t>
+          <t>37709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>60077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112126</t>
+          <t>112361</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128045</t>
+          <t>128797</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129147</t>
+          <t>128420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143563</t>
+          <t>143251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246546</t>
+          <t>246197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269301</t>
+          <t>268565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>778</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19815</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>23805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17178</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23180</t>
+          <t>23398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39187</t>
+          <t>39111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46545</t>
+          <t>46397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17422</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31277</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38921</t>
+          <t>39009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31778</t>
+          <t>31323</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38632</t>
+          <t>38545</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66424</t>
+          <t>65793</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76451</t>
+          <t>76017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15028</t>
+          <t>14094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21063</t>
+          <t>21421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26473</t>
+          <t>26533</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24373</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40393</t>
+          <t>41327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49653</t>
+          <t>49837</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24190</t>
+          <t>24515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30997</t>
+          <t>31222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24745</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29571</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50850</t>
+          <t>52026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59720</t>
+          <t>59968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25228</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104533</t>
+          <t>104797</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116166</t>
+          <t>117068</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99141</t>
+          <t>98885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111589</t>
+          <t>111791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207705</t>
+          <t>208473</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225509</t>
+          <t>225537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15078</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>12429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>23294</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10763</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18995</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29462</t>
+          <t>30207</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40552</t>
+          <t>41072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>28548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28040</t>
+          <t>26389</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>44135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>24375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35926</t>
+          <t>36227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35045</t>
+          <t>35261</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47888</t>
+          <t>48403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62370</t>
+          <t>63916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80011</t>
+          <t>81662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26915</t>
+          <t>27467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26289</t>
+          <t>26674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48977</t>
+          <t>48919</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50156</t>
+          <t>49604</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71664</t>
+          <t>72122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30634</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43935</t>
+          <t>44266</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85017</t>
+          <t>85075</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115205</t>
+          <t>117256</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>30149</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23785</t>
+          <t>23845</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16514</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>25206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>34221</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47056</t>
+          <t>47142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,24%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29750</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65193</t>
+          <t>64467</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49952</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73332</t>
+          <t>72760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86563</t>
+          <t>85984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129050</t>
+          <t>130359</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>113248</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147965</t>
+          <t>147134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108869</t>
+          <t>109441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>132174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230866</t>
+          <t>229557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>273932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16_n_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R2-Habitat-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si consumen más de dos medicamentos en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si han consumido más de dos medicamentos en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10503</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6790</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15412</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>53,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12286</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7776</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17078</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8402</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17187</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>37,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10503</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6409</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15324</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>36,63%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>16715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29800</t>
+          <t>28737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18171</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13262</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21884</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>63,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>46,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>76,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20532</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15740</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25042</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15631</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24416</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>62,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>47,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18171</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13350</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22265</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>63,37%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>32755</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>44777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12447</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7919</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17145</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19,17%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>41,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16259</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11329</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21205</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11915</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21788</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>39,04%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>27,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>50,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12447</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8326</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17231</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>30,13%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22340</t>
+          <t>21810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>36094</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28859</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24161</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33387</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>69,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>58,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>80,83%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>25388</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20442</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30318</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>19859</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>29732</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>60,96%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>72,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>28859</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>24075</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>32980</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>69,87%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46768</t>
+          <t>46858</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60612</t>
+          <t>61142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,71%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16606</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12291</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21610</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,99%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>61,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8049</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4577</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11747</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12026</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>31,99%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16606</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11740</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>21247</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>47,28%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30744</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18517</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13513</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22832</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>52,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>38,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>65,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>17115</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13417</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20587</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13138</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>19981</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>68,01%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>53,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>81,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18517</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>13876</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23383</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>52,72%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>29828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41746</t>
+          <t>41760</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,27%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17708</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12331</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22658</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>58,37%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11343</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7499</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15961</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7482</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15888</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>44,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>62,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17708</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>13229</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>23501</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>45,62%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>22972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35146</t>
+          <t>35711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21109</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16159</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>26486</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>41,63%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>14334</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9716</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18178</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>9789</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>18195</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>55,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>37,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>21109</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>15316</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>25588</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>54,38%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>28783</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41612</t>
+          <t>41522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,38%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>57263</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>48060</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66398</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,39%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>46,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>47937</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>39714</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>57125</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>39115</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>57055</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>38,26%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,59%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>57263</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>48140</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>66271</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>39,79%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92190</t>
+          <t>92603</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118258</t>
+          <t>119116</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>86656</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>77521</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>95859</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>53,86%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>66,61%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>77368</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>68180</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>85591</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>68250</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>86190</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>61,74%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>54,41%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>86656</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>77648</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>95779</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>60,21%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150966</t>
+          <t>150108</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>177034</t>
+          <t>176621</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si consumen más de dos medicamentos en 2012 (tasa de respuesta: 99,54%)</t>
+          <t>Menores según si han consumido más de dos medicamentos en las últimas 2 semanas en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6411</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11254</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18,62%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8405</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4778</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13474</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4332</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13550</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>26,73%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6411</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2939</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10828</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>18,62%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21303</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28013</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23170</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31088</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>81,38%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>23041</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17972</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26668</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17896</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27114</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>73,27%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57,15%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28013</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>23596</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>31485</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>81,38%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44567</t>
+          <t>44476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56567</t>
+          <t>56384</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4675</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9866</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,47%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5407</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2540</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9601</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2488</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10096</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13,03%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,13%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4675</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9439</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35645</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30454</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38248</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75,53%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>36097</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>31903</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>38964</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>31408</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39016</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>86,97%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35645</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>30881</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>38331</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,41%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65990</t>
+          <t>65627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76073</t>
+          <t>75654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41504</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41504</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41504</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3309</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1217</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5975</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2999</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9811</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3218</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10240</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18,13%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3309</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1215</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7027</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33292</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29553</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35384</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,74%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>26989</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23153</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>29965</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22724</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>29746</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>81,87%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33292</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>29574</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>35386</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,96%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54709</t>
+          <t>55494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64108</t>
+          <t>64538</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>36601</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>36601</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>36601</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>36601</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>36601</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>36601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7450</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4178</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12686</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6683</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3099</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11419</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3493</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11493</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7450</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3971</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12370</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21707</t>
+          <t>21237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>39779</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34543</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43051</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>35103</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>30367</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>38687</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>30293</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>38293</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>72,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>39779</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>34859</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>43258</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>84,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67308</t>
+          <t>67778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80013</t>
+          <t>79755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21844</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15257</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30041</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>26470</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18904</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35340</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19392</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>34820</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,92%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>21844</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>15323</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30154</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,78%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37709</t>
+          <t>38212</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60077</t>
+          <t>60635</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>136730</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>128533</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143317</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,22%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,38%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>121231</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>112361</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>128797</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>112881</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128309</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>82,08%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>136730</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>128420</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143251</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,22%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246197</t>
+          <t>245639</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>268565</t>
+          <t>268062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147701</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si consumen más de dos medicamentos en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si han consumido más de dos medicamentos en las últimas 2 semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3183</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,39%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1791</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4682</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,35%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3183</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6940</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20993</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17070</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23369</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>86,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>70,61%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22568</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19677</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23805</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19833</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23799</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,65%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>80,78%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20993</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17236</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23398</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>86,83%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39111</t>
+          <t>39027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>46324</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5254</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2550</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9818</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6790</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11004</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11046</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>15,9%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5254</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2602</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9824</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>17220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35893</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31329</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38597</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>35909</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>31695</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39009</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>31653</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39099</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>84,1%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35893</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>31323</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>38545</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,23%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65793</t>
+          <t>66626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76017</t>
+          <t>76469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6545</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3721</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10975</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>39,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3026</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6194</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6989</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3270</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10577</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>14970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21261</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16831</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24085</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>76,46%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>60,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>24589</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21421</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26533</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20626</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>26484</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21261</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>17229</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>24536</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>76,46%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41327</t>
+          <t>40451</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49837</t>
+          <t>49730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5295</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4382</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1566</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8273</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1635</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8796</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5375</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28131</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24851</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29543</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>28406</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24515</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31222</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>23992</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>31153</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>74,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>28131</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>24771</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>29542</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>52026</t>
+          <t>51328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59968</t>
+          <t>59619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,74 +5989,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16998</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11520</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23909</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>15989</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10393</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22664</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10223</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>22667</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>12,54%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>17,78%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>16998</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>11485</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>24391</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>19,79%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>51</t>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>24849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42264</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>106278</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>99367</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>111756</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>80,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>111472</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>104797</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>117068</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>104794</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>117238</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>87,46%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>82,22%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>106278</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>98885</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>111791</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,21%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>80,21%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>208473</t>
+          <t>207826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225537</t>
+          <t>225888</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si consumen más de dos medicamentos en 2023 (tasa de respuesta: 99,58%)</t>
+          <t>Menores según si han consumido más de dos medicamentos en las últimas 2 semanas en 2023 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6876</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3723</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10920</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>44,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10721</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6735</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14747</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>41,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18109</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>24119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17746</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13702</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20899</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>72,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>55,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15120</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11094</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19106</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>58,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>42,93%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>73,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>15004</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23604</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>35392</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30207</t>
+          <t>26810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41072</t>
+          <t>37748</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>74,12%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19806</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13609</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25945</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24,1%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>45,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13751</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8015</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19867</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>31,08%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,12%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>32318</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26389</t>
+          <t>24649</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44135</t>
+          <t>40334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36652</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30513</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42849</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>54,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,9%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>30491</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24375</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36227</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>68,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,88%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42002</t>
+          <t>23624</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35261</t>
+          <t>18422</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48403</t>
+          <t>27773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>72493</t>
+          <t>60276</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63916</t>
+          <t>52260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81662</t>
+          <t>67945</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>73,38%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17363</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11605</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24483</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,76%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>15648</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4949</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27467</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12657</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26674</t>
+          <t>21504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>35055</t>
+          <t>32946</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16738</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48919</t>
+          <t>42270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34992</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27872</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40750</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>66,84%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>53,24%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>77,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>61423</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>49604</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>72122</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>79,7%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>64,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,58%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37516</t>
+          <t>35242</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30249</t>
+          <t>29322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44266</t>
+          <t>40234</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>98939</t>
+          <t>70235</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85075</t>
+          <t>60911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117256</t>
+          <t>78340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>75,92%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11910</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7869</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16916</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>53,67%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10543</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6716</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14977</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>34,5%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>23145</t>
+          <t>22138</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17228</t>
+          <t>15667</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30149</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19607</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14601</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23648</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>46,33%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>75,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>20018</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>15584</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23845</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>65,5%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25206</t>
+          <t>23481</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>41225</t>
+          <t>39102</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34221</t>
+          <t>32320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47142</t>
+          <t>45573</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>74,42%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>55955</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46133</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66628</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>50663</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30581</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>64467</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>61204</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50027</t>
+          <t>40244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72760</t>
+          <t>58311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>111868</t>
+          <t>105583</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85984</t>
+          <t>93209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130359</t>
+          <t>120878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>108997</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>98324</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>118819</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>59,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>127052</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>113248</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>147134</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>71,49%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>63,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,79%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>120997</t>
+          <t>93364</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109441</t>
+          <t>84681</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132174</t>
+          <t>102748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>248048</t>
+          <t>202361</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>229557</t>
+          <t>187066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273932</t>
+          <t>214735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
